--- a/Revenue Report/Revenue_Report_July_2026_H1.xlsx
+++ b/Revenue Report/Revenue_Report_July_2026_H1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>Period</t>
   </si>
@@ -296,16 +296,10 @@
     <t>July 2026 H1  (2026-07-01 to 2026-07-14 inclusive)</t>
   </si>
   <si>
-    <t>Run date (UTC)</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:14:53</t>
+    <t>2026-07-16 10:03:14</t>
   </si>
   <si>
     <t>Source</t>
@@ -1223,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.45703125" customWidth="true" bestFit="true"/>
@@ -1280,34 +1274,26 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="1">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Revenue Report/Revenue_Report_July_2026_H1.xlsx
+++ b/Revenue Report/Revenue_Report_July_2026_H1.xlsx
@@ -299,7 +299,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:14</t>
+    <t>2026-07-16 15:22:47</t>
   </si>
   <si>
     <t>Source</t>

--- a/Revenue Report/Revenue_Report_July_2026_H1.xlsx
+++ b/Revenue Report/Revenue_Report_July_2026_H1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="129">
   <si>
     <t>Period</t>
   </si>
@@ -32,25 +32,25 @@
     <t>Jobs completed</t>
   </si>
   <si>
-    <t>7</t>
+    <t>59</t>
   </si>
   <si>
     <t>Jobs cancelled</t>
   </si>
   <si>
-    <t>0</t>
+    <t>3</t>
   </si>
   <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>363,249.40</t>
+    <t>834,356.16</t>
   </si>
   <si>
     <t>Customers served</t>
   </si>
   <si>
-    <t>4</t>
+    <t>18</t>
   </si>
   <si>
     <t>Job</t>
@@ -68,16 +68,178 @@
     <t>Cancelled</t>
   </si>
   <si>
+    <t>JO0025</t>
+  </si>
+  <si>
+    <t>Annual Service Inspection</t>
+  </si>
+  <si>
+    <t>JO0003</t>
+  </si>
+  <si>
+    <t>Wheel Alignment</t>
+  </si>
+  <si>
+    <t>JO0016</t>
+  </si>
+  <si>
+    <t>Exhaust System Repair</t>
+  </si>
+  <si>
+    <t>JO0018</t>
+  </si>
+  <si>
+    <t>Air Conditioning Regas</t>
+  </si>
+  <si>
+    <t>JO0026</t>
+  </si>
+  <si>
+    <t>Emission Test and Certification</t>
+  </si>
+  <si>
+    <t>JO0027</t>
+  </si>
+  <si>
+    <t>Power Steering Fluid Service</t>
+  </si>
+  <si>
+    <t>JO0021</t>
+  </si>
+  <si>
+    <t>Starter Motor Repair</t>
+  </si>
+  <si>
+    <t>JO0004</t>
+  </si>
+  <si>
+    <t>Brake Pad Replacement</t>
+  </si>
+  <si>
+    <t>JO0024</t>
+  </si>
+  <si>
+    <t>Full Vehicle Diagnostic Scan</t>
+  </si>
+  <si>
+    <t>JO0015</t>
+  </si>
+  <si>
+    <t>Shock Absorber Replacement</t>
+  </si>
+  <si>
+    <t>JO0014</t>
+  </si>
+  <si>
+    <t>Suspension Strut Replacement</t>
+  </si>
+  <si>
+    <t>JO0020</t>
+  </si>
+  <si>
+    <t>Alternator Replacement</t>
+  </si>
+  <si>
+    <t>JO0009</t>
+  </si>
+  <si>
+    <t>Spark Plug Replacement</t>
+  </si>
+  <si>
+    <t>JO0011</t>
+  </si>
+  <si>
+    <t>Coolant Flush and Refill</t>
+  </si>
+  <si>
+    <t>JO0023</t>
+  </si>
+  <si>
+    <t>Windscreen Wiper Replacement</t>
+  </si>
+  <si>
+    <t>JO0022</t>
+  </si>
+  <si>
+    <t>Headlight Alignment</t>
+  </si>
+  <si>
+    <t>JO0006</t>
+  </si>
+  <si>
+    <t>Battery Test and Replacement</t>
+  </si>
+  <si>
+    <t>JO0008</t>
+  </si>
+  <si>
+    <t>Cabin Filter Replacement</t>
+  </si>
+  <si>
+    <t>JO0028</t>
+  </si>
+  <si>
+    <t>Fuel Injector Cleaning</t>
+  </si>
+  <si>
+    <t>JO0001</t>
+  </si>
+  <si>
+    <t>Engine Oil and Filter Change</t>
+  </si>
+  <si>
+    <t>JO0030</t>
+  </si>
+  <si>
+    <t>Underbody Rust Treatment</t>
+  </si>
+  <si>
+    <t>JO0002</t>
+  </si>
+  <si>
+    <t>Tyre Rotation and Balancing</t>
+  </si>
+  <si>
     <t>JO0010</t>
   </si>
   <si>
     <t>Timing Belt Replacement</t>
   </si>
   <si>
-    <t>JO0002</t>
-  </si>
-  <si>
-    <t>Tyre Rotation and Balancing</t>
+    <t>JO0013</t>
+  </si>
+  <si>
+    <t>Clutch Inspection and Adjustment</t>
+  </si>
+  <si>
+    <t>JO0017</t>
+  </si>
+  <si>
+    <t>Radiator Repair</t>
+  </si>
+  <si>
+    <t>JO0029</t>
+  </si>
+  <si>
+    <t>Differential Oil Change</t>
+  </si>
+  <si>
+    <t>JO0019</t>
+  </si>
+  <si>
+    <t>AC Compressor Repair</t>
+  </si>
+  <si>
+    <t>JO0005</t>
+  </si>
+  <si>
+    <t>Brake Disc Skimming</t>
+  </si>
+  <si>
+    <t>JO0012</t>
+  </si>
+  <si>
+    <t>Transmission Fluid Service</t>
   </si>
   <si>
     <t>JO0007</t>
@@ -86,168 +248,6 @@
     <t>Air Filter Replacement</t>
   </si>
   <si>
-    <t>JO0018</t>
-  </si>
-  <si>
-    <t>Air Conditioning Regas</t>
-  </si>
-  <si>
-    <t>JO0025</t>
-  </si>
-  <si>
-    <t>Annual Service Inspection</t>
-  </si>
-  <si>
-    <t>JO0014</t>
-  </si>
-  <si>
-    <t>Suspension Strut Replacement</t>
-  </si>
-  <si>
-    <t>JO0012</t>
-  </si>
-  <si>
-    <t>Transmission Fluid Service</t>
-  </si>
-  <si>
-    <t>JO0011</t>
-  </si>
-  <si>
-    <t>Coolant Flush and Refill</t>
-  </si>
-  <si>
-    <t>JO0013</t>
-  </si>
-  <si>
-    <t>Clutch Inspection and Adjustment</t>
-  </si>
-  <si>
-    <t>JO0005</t>
-  </si>
-  <si>
-    <t>Brake Disc Skimming</t>
-  </si>
-  <si>
-    <t>JO0004</t>
-  </si>
-  <si>
-    <t>Brake Pad Replacement</t>
-  </si>
-  <si>
-    <t>JO0023</t>
-  </si>
-  <si>
-    <t>Windscreen Wiper Replacement</t>
-  </si>
-  <si>
-    <t>JO0016</t>
-  </si>
-  <si>
-    <t>Exhaust System Repair</t>
-  </si>
-  <si>
-    <t>JO0022</t>
-  </si>
-  <si>
-    <t>Headlight Alignment</t>
-  </si>
-  <si>
-    <t>JO0008</t>
-  </si>
-  <si>
-    <t>Cabin Filter Replacement</t>
-  </si>
-  <si>
-    <t>JO0029</t>
-  </si>
-  <si>
-    <t>Differential Oil Change</t>
-  </si>
-  <si>
-    <t>JO0028</t>
-  </si>
-  <si>
-    <t>Fuel Injector Cleaning</t>
-  </si>
-  <si>
-    <t>JO0009</t>
-  </si>
-  <si>
-    <t>Spark Plug Replacement</t>
-  </si>
-  <si>
-    <t>JO0024</t>
-  </si>
-  <si>
-    <t>Full Vehicle Diagnostic Scan</t>
-  </si>
-  <si>
-    <t>JO0021</t>
-  </si>
-  <si>
-    <t>Starter Motor Repair</t>
-  </si>
-  <si>
-    <t>JO0027</t>
-  </si>
-  <si>
-    <t>Power Steering Fluid Service</t>
-  </si>
-  <si>
-    <t>JO0003</t>
-  </si>
-  <si>
-    <t>Wheel Alignment</t>
-  </si>
-  <si>
-    <t>JO0006</t>
-  </si>
-  <si>
-    <t>Battery Test and Replacement</t>
-  </si>
-  <si>
-    <t>JO0020</t>
-  </si>
-  <si>
-    <t>Alternator Replacement</t>
-  </si>
-  <si>
-    <t>JO0015</t>
-  </si>
-  <si>
-    <t>Shock Absorber Replacement</t>
-  </si>
-  <si>
-    <t>JO0026</t>
-  </si>
-  <si>
-    <t>Emission Test and Certification</t>
-  </si>
-  <si>
-    <t>JO0001</t>
-  </si>
-  <si>
-    <t>Engine Oil and Filter Change</t>
-  </si>
-  <si>
-    <t>JO0030</t>
-  </si>
-  <si>
-    <t>Underbody Rust Treatment</t>
-  </si>
-  <si>
-    <t>JO0019</t>
-  </si>
-  <si>
-    <t>AC Compressor Repair</t>
-  </si>
-  <si>
-    <t>JO0017</t>
-  </si>
-  <si>
-    <t>Radiator Repair</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -257,16 +257,52 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Visits</t>
+    <t>Vehicles</t>
   </si>
   <si>
     <t>Jobs</t>
   </si>
   <si>
-    <t>CU0025</t>
-  </si>
-  <si>
-    <t>Elizabeth Reed</t>
+    <t>CU0035</t>
+  </si>
+  <si>
+    <t>Paul Green</t>
+  </si>
+  <si>
+    <t>CU0016</t>
+  </si>
+  <si>
+    <t>Dorothy Jones</t>
+  </si>
+  <si>
+    <t>CU0017</t>
+  </si>
+  <si>
+    <t>Anthony Miller</t>
+  </si>
+  <si>
+    <t>CU0018</t>
+  </si>
+  <si>
+    <t>Matthew Stewart</t>
+  </si>
+  <si>
+    <t>CU0005</t>
+  </si>
+  <si>
+    <t>Susan Peterson</t>
+  </si>
+  <si>
+    <t>CU0001</t>
+  </si>
+  <si>
+    <t>Margaret Scott</t>
+  </si>
+  <si>
+    <t>CU0021</t>
+  </si>
+  <si>
+    <t>Kenneth Harris</t>
   </si>
   <si>
     <t>CU0027</t>
@@ -275,16 +311,58 @@
     <t>Paul Cox</t>
   </si>
   <si>
-    <t>CU0053</t>
-  </si>
-  <si>
-    <t>Elizabeth Taylor</t>
-  </si>
-  <si>
-    <t>CU0043</t>
-  </si>
-  <si>
-    <t>Edward Ward</t>
+    <t>CU0014</t>
+  </si>
+  <si>
+    <t>Jason Wright</t>
+  </si>
+  <si>
+    <t>CU0003</t>
+  </si>
+  <si>
+    <t>Rebecca Morgan</t>
+  </si>
+  <si>
+    <t>CU0010</t>
+  </si>
+  <si>
+    <t>Angela Miller</t>
+  </si>
+  <si>
+    <t>CU0034</t>
+  </si>
+  <si>
+    <t>Michael Cox</t>
+  </si>
+  <si>
+    <t>CU0032</t>
+  </si>
+  <si>
+    <t>Larry Allen</t>
+  </si>
+  <si>
+    <t>CU0004</t>
+  </si>
+  <si>
+    <t>Jonathan Nelson</t>
+  </si>
+  <si>
+    <t>CU0033</t>
+  </si>
+  <si>
+    <t>Sandra Peterson</t>
+  </si>
+  <si>
+    <t>CU0028</t>
+  </si>
+  <si>
+    <t>Steven Cook</t>
+  </si>
+  <si>
+    <t>CU0011</t>
+  </si>
+  <si>
+    <t>Anna Green</t>
   </si>
   <si>
     <t>Report</t>
@@ -299,7 +377,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 15:22:47</t>
+    <t>2026-07-23 07:38:20</t>
   </si>
   <si>
     <t>Source</t>
@@ -311,7 +389,7 @@
     <t>Basis</t>
   </si>
   <si>
-    <t>Job assignments completed within the period (jobassign_status = 'C')</t>
+    <t>Jobs completed within the period (status = 'C'), keyed on updated_at</t>
   </si>
   <si>
     <t>Note</t>
@@ -323,7 +401,7 @@
     <t>Total revenue</t>
   </si>
   <si>
-    <t>363249.40</t>
+    <t>834356.16</t>
   </si>
 </sst>
 </file>
@@ -494,13 +572,13 @@
         <v>18</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" t="n" s="2">
-        <v>99195.17</v>
+        <v>81133.33</v>
       </c>
       <c r="E2" t="n" s="2">
-        <v>49597.59</v>
+        <v>16226.67</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>0.0</v>
@@ -514,13 +592,13 @@
         <v>20</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="D3" t="n" s="2">
-        <v>82726.61</v>
+        <v>79148.98</v>
       </c>
       <c r="E3" t="n" s="2">
-        <v>82726.61</v>
+        <v>13191.5</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>0.0</v>
@@ -534,13 +612,13 @@
         <v>22</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D4" t="n" s="2">
-        <v>82300.05</v>
+        <v>55900.0</v>
       </c>
       <c r="E4" t="n" s="2">
-        <v>82300.05</v>
+        <v>18633.33</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>0.0</v>
@@ -554,13 +632,13 @@
         <v>24</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D5" t="n" s="2">
-        <v>50158.57</v>
+        <v>54702.38</v>
       </c>
       <c r="E5" t="n" s="2">
-        <v>50158.57</v>
+        <v>18234.13</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>0.0</v>
@@ -574,13 +652,13 @@
         <v>26</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D6" t="n" s="2">
-        <v>36163.41</v>
+        <v>51644.88</v>
       </c>
       <c r="E6" t="n" s="2">
-        <v>36163.41</v>
+        <v>12911.22</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>0.0</v>
@@ -594,13 +672,13 @@
         <v>28</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D7" t="n" s="2">
-        <v>12705.59</v>
+        <v>51490.24</v>
       </c>
       <c r="E7" t="n" s="2">
-        <v>12705.59</v>
+        <v>12872.56</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>0.0</v>
@@ -614,13 +692,13 @@
         <v>30</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D8" t="n" s="2">
-        <v>0.0</v>
+        <v>45041.29</v>
       </c>
       <c r="E8" t="n" s="2">
-        <v>0.0</v>
+        <v>15013.76</v>
       </c>
       <c r="F8" t="n" s="0">
         <v>0.0</v>
@@ -634,13 +712,13 @@
         <v>32</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D9" t="n" s="2">
-        <v>0.0</v>
+        <v>35344.4</v>
       </c>
       <c r="E9" t="n" s="2">
-        <v>0.0</v>
+        <v>17672.2</v>
       </c>
       <c r="F9" t="n" s="0">
         <v>0.0</v>
@@ -654,13 +732,13 @@
         <v>34</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D10" t="n" s="2">
-        <v>0.0</v>
+        <v>33361.95</v>
       </c>
       <c r="E10" t="n" s="2">
-        <v>0.0</v>
+        <v>16680.98</v>
       </c>
       <c r="F10" t="n" s="0">
         <v>0.0</v>
@@ -674,13 +752,13 @@
         <v>36</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D11" t="n" s="2">
-        <v>0.0</v>
+        <v>31708.2</v>
       </c>
       <c r="E11" t="n" s="2">
-        <v>0.0</v>
+        <v>15854.1</v>
       </c>
       <c r="F11" t="n" s="0">
         <v>0.0</v>
@@ -694,13 +772,13 @@
         <v>38</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D12" t="n" s="2">
-        <v>0.0</v>
+        <v>30178.61</v>
       </c>
       <c r="E12" t="n" s="2">
-        <v>0.0</v>
+        <v>15089.31</v>
       </c>
       <c r="F12" t="n" s="0">
         <v>0.0</v>
@@ -714,13 +792,13 @@
         <v>40</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D13" t="n" s="2">
-        <v>0.0</v>
+        <v>27388.96</v>
       </c>
       <c r="E13" t="n" s="2">
-        <v>0.0</v>
+        <v>13694.48</v>
       </c>
       <c r="F13" t="n" s="0">
         <v>0.0</v>
@@ -734,13 +812,13 @@
         <v>42</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D14" t="n" s="2">
-        <v>0.0</v>
+        <v>25616.78</v>
       </c>
       <c r="E14" t="n" s="2">
-        <v>0.0</v>
+        <v>8538.93</v>
       </c>
       <c r="F14" t="n" s="0">
         <v>0.0</v>
@@ -754,13 +832,13 @@
         <v>44</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D15" t="n" s="2">
-        <v>0.0</v>
+        <v>25598.91</v>
       </c>
       <c r="E15" t="n" s="2">
-        <v>0.0</v>
+        <v>12799.46</v>
       </c>
       <c r="F15" t="n" s="0">
         <v>0.0</v>
@@ -774,13 +852,13 @@
         <v>46</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D16" t="n" s="2">
-        <v>0.0</v>
+        <v>24920.1</v>
       </c>
       <c r="E16" t="n" s="2">
-        <v>0.0</v>
+        <v>12460.05</v>
       </c>
       <c r="F16" t="n" s="0">
         <v>0.0</v>
@@ -794,16 +872,16 @@
         <v>48</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D17" t="n" s="2">
-        <v>0.0</v>
+        <v>24760.82</v>
       </c>
       <c r="E17" t="n" s="2">
-        <v>0.0</v>
+        <v>12380.41</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -814,16 +892,16 @@
         <v>50</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D18" t="n" s="2">
-        <v>0.0</v>
+        <v>22884.6</v>
       </c>
       <c r="E18" t="n" s="2">
-        <v>0.0</v>
+        <v>22884.6</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -834,13 +912,13 @@
         <v>52</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D19" t="n" s="2">
-        <v>0.0</v>
+        <v>22365.7</v>
       </c>
       <c r="E19" t="n" s="2">
-        <v>0.0</v>
+        <v>22365.7</v>
       </c>
       <c r="F19" t="n" s="0">
         <v>0.0</v>
@@ -854,13 +932,13 @@
         <v>54</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D20" t="n" s="2">
-        <v>0.0</v>
+        <v>20603.05</v>
       </c>
       <c r="E20" t="n" s="2">
-        <v>0.0</v>
+        <v>10301.53</v>
       </c>
       <c r="F20" t="n" s="0">
         <v>0.0</v>
@@ -874,13 +952,13 @@
         <v>56</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D21" t="n" s="2">
-        <v>0.0</v>
+        <v>17271.08</v>
       </c>
       <c r="E21" t="n" s="2">
-        <v>0.0</v>
+        <v>17271.08</v>
       </c>
       <c r="F21" t="n" s="0">
         <v>0.0</v>
@@ -894,13 +972,13 @@
         <v>58</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" t="n" s="2">
-        <v>0.0</v>
+        <v>17248.99</v>
       </c>
       <c r="E22" t="n" s="2">
-        <v>0.0</v>
+        <v>17248.99</v>
       </c>
       <c r="F22" t="n" s="0">
         <v>0.0</v>
@@ -914,13 +992,13 @@
         <v>60</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="D23" t="n" s="2">
-        <v>0.0</v>
+        <v>15836.71</v>
       </c>
       <c r="E23" t="n" s="2">
-        <v>0.0</v>
+        <v>7918.36</v>
       </c>
       <c r="F23" t="n" s="0">
         <v>0.0</v>
@@ -934,13 +1012,13 @@
         <v>62</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D24" t="n" s="2">
-        <v>0.0</v>
+        <v>13139.85</v>
       </c>
       <c r="E24" t="n" s="2">
-        <v>0.0</v>
+        <v>13139.85</v>
       </c>
       <c r="F24" t="n" s="0">
         <v>0.0</v>
@@ -954,16 +1032,16 @@
         <v>64</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D25" t="n" s="2">
-        <v>0.0</v>
+        <v>10748.76</v>
       </c>
       <c r="E25" t="n" s="2">
-        <v>0.0</v>
+        <v>10748.76</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
@@ -974,13 +1052,13 @@
         <v>66</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D26" t="n" s="2">
-        <v>0.0</v>
+        <v>9052.33</v>
       </c>
       <c r="E26" t="n" s="2">
-        <v>0.0</v>
+        <v>9052.33</v>
       </c>
       <c r="F26" t="n" s="0">
         <v>0.0</v>
@@ -994,13 +1072,13 @@
         <v>68</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D27" t="n" s="2">
-        <v>0.0</v>
+        <v>7265.26</v>
       </c>
       <c r="E27" t="n" s="2">
-        <v>0.0</v>
+        <v>7265.26</v>
       </c>
       <c r="F27" t="n" s="0">
         <v>0.0</v>
@@ -1091,13 +1169,13 @@
         <v>77</v>
       </c>
       <c r="C32" t="n" s="4">
-        <v>7.0</v>
+        <v>59.0</v>
       </c>
       <c r="D32" t="n" s="3">
-        <v>363249.4000000001</v>
+        <v>834356.1599999998</v>
       </c>
       <c r="F32" t="n" s="4">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -1107,12 +1185,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.6640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.83203125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.53125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="12.78515625" customWidth="true" bestFit="true"/>
   </cols>
@@ -1135,79 +1213,313 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>83</v>
-      </c>
+      <c r="A2" s="0"/>
+      <c r="B2" s="0"/>
       <c r="C2" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="E2" t="n" s="2">
-        <v>218085.19</v>
+        <v>207540.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E3" t="n" s="2">
-        <v>82300.05</v>
+        <v>118110.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E4" t="n" s="2">
-        <v>50158.57</v>
+        <v>73538.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E5" t="n" s="2">
+        <v>71433.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B6" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="C5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E5" t="n" s="2">
-        <v>12705.59</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="4">
+      <c r="C6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E6" t="n" s="2">
+        <v>60036.46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="E7" t="n" s="2">
+        <v>52511.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E8" t="n" s="2">
+        <v>40784.21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E9" t="n" s="2">
+        <v>33516.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E10" t="n" s="2">
+        <v>32249.02</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="n" s="2">
+        <v>26666.93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E12" t="n" s="2">
+        <v>21851.22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E13" t="n" s="2">
+        <v>17718.29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E14" t="n" s="2">
+        <v>17248.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E15" t="n" s="2">
+        <v>17239.42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D16" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="n" s="2">
+        <v>15954.37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="n" s="2">
+        <v>11562.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E18" t="n" s="2">
+        <v>9052.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E19" t="n" s="2">
+        <v>7340.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
         <v>77</v>
       </c>
-      <c r="E6" t="n" s="3">
-        <v>363249.4</v>
+      <c r="E20" t="n" s="3">
+        <v>834356.16</v>
       </c>
     </row>
   </sheetData>
@@ -1226,10 +1538,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2">
@@ -1237,39 +1549,39 @@
         <v>0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>92</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>94</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -1290,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
